--- a/docs/business-plan/PREVISIONNEL_FINANCIER_NEXUS.xlsx
+++ b/docs/business-plan/PREVISIONNEL_FINANCIER_NEXUS.xlsx
@@ -26,8 +26,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0 €"/>
-    <numFmt numFmtId="165" formatCode="#,##0 €;[Red]-#,##0 €"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0 €;[Red]-#,##0 €"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -71,7 +71,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -108,12 +108,6 @@
         <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE8E6"/>
-        <bgColor rgb="00FCE8E6"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -141,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,34 +143,35 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,12 +538,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,28 +580,32 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Prix Starter (EUR/mois)</t>
+          <t>Prix Free (EUR/mois)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Abonnement mensuel</t>
+          <t>Gratuit a vie</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Prix Pro (EUR/mois)</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>249</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
+          <t>Prix Basic (EUR/mois)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Illimite + 1000 credits IA/mois</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -614,38 +613,42 @@
           <t>Prix Business (EUR/mois)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
+      <c r="B7" s="7" t="n">
+        <v>149</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Multi-site + 10000 credits IA/mois</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Mix Starter (%)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>0.5</v>
+          <t>Mix Free (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>0.1</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Part des clients Starter</t>
+          <t>Utilisateurs gratuits</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Mix Pro (%)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>0.35</v>
+          <t>Mix Basic (%)</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>0.7</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Part des clients Pro</t>
+          <t>Coeur de cible PME</t>
         </is>
       </c>
     </row>
@@ -655,12 +658,12 @@
           <t>Mix Business (%)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
-        <v>0.15</v>
+      <c r="B10" s="8" t="n">
+        <v>0.2</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Part des clients Business</t>
+          <t>Multi-sites, franchises</t>
         </is>
       </c>
     </row>
@@ -670,7 +673,7 @@
           <t>ARPA (revenu moyen/client/mois)</t>
         </is>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="7">
         <f>B5*B8+B6*B9+B7*B10</f>
         <v/>
       </c>
@@ -680,8 +683,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr"/>
-      <c r="B12" s="8" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
@@ -690,7 +693,7 @@
           <t>Churn mensuel An 1</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="9" t="n">
         <v>0.03</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -705,7 +708,7 @@
           <t>Churn mensuel An 2</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B14" s="9" t="n">
         <v>0.025</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -720,7 +723,7 @@
           <t>Churn mensuel An 3</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
         <v>0.02</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -730,222 +733,245 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr"/>
-      <c r="B16" s="8" t="inlineStr"/>
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Cout hebergement/client (EUR/mois)</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>8</v>
+          <t>Cout infra fixe (EUR/mois)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>150</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Render + Supabase + Twilio</t>
+          <t>Render + Supabase base</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Cout variable/client (EUR/mois)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Anthropic + Twilio + Resend</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>Commission Stripe (%)</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>1.4% + 0.25 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr"/>
-      <c r="B19" s="8" t="inlineStr"/>
-      <c r="C19" s="6" t="inlineStr"/>
+      <c r="B19" s="9" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Salaire fondateur net (EUR/mois)</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Phase demarrage</t>
-        </is>
-      </c>
+      <c r="A20" s="5" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Salaire dev brut (EUR/mois)</t>
+          <t>Salaire fondateur M1-M6</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>3333</v>
+        <v>0</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>40k brut annuel</t>
+          <t>Pas de salaire les 6 premiers mois</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Salaire commercial brut (EUR/mois)</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>2667</v>
+          <t>Salaire fondateur M7+ An 1 (EUR/mois)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>1200</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>32k brut annuel</t>
+          <t>Phase demarrage</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Taux charges sociales</t>
+          <t>Salaire fondateur An 2 (EUR/mois)</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>0.45</v>
+        <v>2000</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Regime general</t>
+          <t>Croissance</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr"/>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr"/>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Salaire fondateur An 3 (EUR/mois)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Rentabilite</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Loyer/coworking (EUR/mois)</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr"/>
+          <t>Taux charges sociales</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>SASU regime general</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Assurances (EUR/mois)</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>RC Pro + Cyber</t>
-        </is>
-      </c>
+      <c r="A26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Comptable/juridique (EUR/mois)</t>
+          <t>Comptable / juridique</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>250</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Fondateur = comptable (BEP + 10 ans exp)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Marketing M1-M3 (EUR/mois)</t>
+          <t>Loyer</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Demarrage</t>
+          <t>Societe hebergee au domicile du fondateur</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Marketing M4+ (EUR/mois)</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>1000</v>
+          <t>Marketing An 1 (EUR/mois)</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>300</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Acceleration</t>
+          <t>Reseaux sociaux + pub ciblee</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr"/>
-      <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="6" t="inlineStr"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Marketing An 2+ (EUR/mois)</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>800</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Ads + partenariats</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>TVA</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Taux standard</t>
-        </is>
-      </c>
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>IS taux reduit (&lt; 42500 EUR)</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n">
-        <v>0.15</v>
+          <t>TVA</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>0.2</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>PME</t>
+          <t>Taux standard</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>IS taux reduit (&lt; 42500 EUR)</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>PME</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>IS taux normal</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n">
+      <c r="B34" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>Au-dela de 42500 EUR</t>
         </is>
@@ -967,30 +993,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="3" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PLAN DE FINANCEMENT INITIAL</t>
+          <t>PLAN DE FINANCEMENT INITIAL — 40 000 EUR (+ NACRE 5K optionnel)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>BESOINS</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>RESSOURCES</t>
         </is>
@@ -1020,163 +1046,155 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Developpement logiciel (capitalise)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Fonds de roulement (6 mois charges mini)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Capital social SASU</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Tresorerie de securite (couverture pertes Y1)</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Apport en nature (logiciel NEXUS v3.25)</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Marketing lancement (reseaux, pub ciblee)</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Pret d'honneur Initiative 95</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Capital social SASU</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Licences et outils</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Pret d'honneur Initiative 95</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Materiel informatique</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B8" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Pret bancaire (garanti BPI 60%)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Frais d'etablissement (SASU, juridique)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>NACRE phase 2 (OPTIONNEL)</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Pret d'honneur WILCO</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Frais d'etablissement</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Pret bancaire (garanti BPI 60%)</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>BFR de demarrage</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>NACRE phase 2 (ASS)</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Tresorerie de securite</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Subventions (BPI/Region)</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Marketing lancement</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Recrutement (3 mois avance)</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>15000</v>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL BESOINS</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
+        <f>SUM(B5:B9)</f>
+        <v/>
+      </c>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL TRESORERIE BASE (sans NACRE)</t>
+        </is>
+      </c>
+      <c r="E11" s="14">
+        <f>E7+E8</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL BESOINS</t>
-        </is>
-      </c>
-      <c r="B13" s="13">
-        <f>SUM(B5:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>TOTAL RESSOURCES</t>
-        </is>
-      </c>
-      <c r="E13" s="13">
-        <f>SUM(E5:E12)</f>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Equilibre (Ressources tresorerie - Besoins)</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>E11-B11</f>
+        <v/>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL AVEC NACRE (optionnel)</t>
+        </is>
+      </c>
+      <c r="E13" s="17">
+        <f>E7+E8+E9</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Equilibre (Ressources - Besoins)</t>
-        </is>
-      </c>
-      <c r="B15" s="15">
-        <f>E13-B13</f>
-        <v/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Note : L'apport en nature (80 000 EUR) valorise le logiciel developpe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>pendant 18 mois. Il n'apporte pas de tresorerie mais renforce les fonds propres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>NACRE = gere par la Region (pas France Travail). Bonus si eligible, pas indispensable.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1258,21 +1276,21 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17">
+      <c r="B5" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19">
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="12">
         <f>D5*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="12">
         <f>E5*12</f>
         <v/>
       </c>
@@ -1283,21 +1301,21 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="17">
+      <c r="B6" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="19">
         <f>D5+B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="12">
         <f>D6*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <f>E6*12</f>
         <v/>
       </c>
@@ -1308,21 +1326,21 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="17">
+      <c r="B7" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19">
         <f>D6+B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="12">
         <f>D7*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="12">
         <f>E7*12</f>
         <v/>
       </c>
@@ -1333,21 +1351,21 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="17">
+      <c r="B8" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19">
         <f>D7+B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="12">
         <f>D8*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="12">
         <f>E8*12</f>
         <v/>
       </c>
@@ -1358,21 +1376,21 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="17">
+      <c r="B9" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="19">
         <f>D8+B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="12">
         <f>D9*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="12">
         <f>E9*12</f>
         <v/>
       </c>
@@ -1383,21 +1401,21 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="19">
         <f>D9+B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="12">
         <f>D10*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="12">
         <f>E10*12</f>
         <v/>
       </c>
@@ -1408,21 +1426,21 @@
           <t>M7</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="19">
         <f>D10+B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="12">
         <f>D11*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="12">
         <f>E11*12</f>
         <v/>
       </c>
@@ -1433,21 +1451,21 @@
           <t>M8</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="17">
+      <c r="B12" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="19">
         <f>D11+B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="12">
         <f>D12*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="12">
         <f>E12*12</f>
         <v/>
       </c>
@@ -1458,21 +1476,21 @@
           <t>M9</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="17">
+      <c r="B13" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="19">
         <f>D12+B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="12">
         <f>D13*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="12">
         <f>E13*12</f>
         <v/>
       </c>
@@ -1483,21 +1501,21 @@
           <t>M10</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="17">
+      <c r="B14" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="19">
         <f>D13+B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="12">
         <f>D14*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="12">
         <f>E14*12</f>
         <v/>
       </c>
@@ -1508,21 +1526,21 @@
           <t>M11</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="17">
+      <c r="B15" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="19">
         <f>D14+B15-C15</f>
         <v/>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="12">
         <f>D15*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="12">
         <f>E15*12</f>
         <v/>
       </c>
@@ -1533,82 +1551,82 @@
           <t>M12</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="17">
+      <c r="B16" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="19">
         <f>D15+B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="12">
         <f>D16*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="12">
         <f>E16*12</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Total An 1</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="14">
         <f>SUM(B5:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="14">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="14">
         <f>D16</f>
         <v/>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="14">
         <f>E16</f>
         <v/>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>F16</f>
         <v/>
       </c>
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>An 2 (previsions)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Nouveaux clients</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
-        <v>120</v>
+      <c r="B20" s="21" t="n">
+        <v>278</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Churn total</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
-        <v>17</v>
+      <c r="B21" s="21" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Clients fin An 2</t>
         </is>
@@ -1619,46 +1637,46 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>MRR fin An 2</t>
         </is>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="22">
         <f>B22*Hypotheses!B11</f>
         <v/>
       </c>
     </row>
     <row r="24"/>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>An 3 (previsions)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Nouveaux clients</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
-        <v>144</v>
+      <c r="B26" s="21" t="n">
+        <v>285</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Churn total</t>
         </is>
       </c>
-      <c r="B27" s="19" t="n">
-        <v>34</v>
+      <c r="B27" s="21" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Clients fin An 3</t>
         </is>
@@ -1669,12 +1687,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>MRR fin An 3</t>
         </is>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="22">
         <f>B28*Hypotheses!B11</f>
         <v/>
       </c>
@@ -1714,7 +1732,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lie aux onglets Hypotheses et Clients &amp; MRR</t>
+          <t>Lie aux onglets Hypotheses et Clients &amp; MRR — Solo founder An 1/An 2, 1er recrutement An 3</t>
         </is>
       </c>
     </row>
@@ -1741,133 +1759,133 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>PRODUITS D'EXPLOITATION</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Abonnements SaaS (HT)</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n">
-        <v>71640</v>
-      </c>
-      <c r="C7" s="21" t="n">
-        <v>238800</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>477600</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Abonnements SaaS + credits IA (HT)</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>35860</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>149710</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>309700</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Setup fees / accompagnement</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C8" s="21" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>15000</v>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Setup / accompagnement</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>13500</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>16000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TOTAL CA HT</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="14">
         <f>B7+B8</f>
         <v/>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="14">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="14">
         <f>D7+D8</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>CHARGES VARIABLES</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Hebergement cloud</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C12" s="21" t="n">
-        <v>9600</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>18000</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Hebergement cloud (Render, Supabase)</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Services tiers (Twilio/Resend/Anthropic)</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="n">
-        <v>4800</v>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>14400</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>28800</v>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Services tiers (Anthropic, Twilio, Resend)</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>24000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Commissions Stripe</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="n">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Commissions Stripe (2.9%)</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
         <v>1200</v>
       </c>
-      <c r="C14" s="21" t="n">
-        <v>3800</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>7500</v>
+      <c r="C14" s="23" t="n">
+        <v>4700</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>9500</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Total charges variables</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="14">
         <f>SUM(B12:B14)</f>
         <v/>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="14">
         <f>SUM(C12:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="14">
         <f>SUM(D12:D14)</f>
         <v/>
       </c>
@@ -1878,244 +1896,240 @@
           <t>MARGE BRUTE</t>
         </is>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="24">
         <f>B9-B15</f>
         <v/>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="24">
         <f>C9-C15</f>
         <v/>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="24">
         <f>D9-D15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Taux de marge brute</t>
         </is>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="25">
         <f>B17/B9</f>
         <v/>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="25">
         <f>C17/C9</f>
         <v/>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="25">
         <f>D17/D9</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>CHARGES FIXES</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Salaire fondateur</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="n">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Remuneration fondateur (net)</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n">
+        <v>7200</v>
+      </c>
+      <c r="C21" s="23" t="n">
         <v>24000</v>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="D21" s="23" t="n">
         <v>36000</v>
       </c>
-      <c r="D21" s="21" t="n">
-        <v>42000</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Salaire developpeur (M4)</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C22" s="21" t="n">
-        <v>48000</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>52000</v>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Charges sociales (45%)</t>
+        </is>
+      </c>
+      <c r="B22" s="23">
+        <f>B21*Hypotheses!B25</f>
+        <v/>
+      </c>
+      <c r="C22" s="23">
+        <f>C21*Hypotheses!B25</f>
+        <v/>
+      </c>
+      <c r="D22" s="23">
+        <f>D21*Hypotheses!B25</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Salaire commercial (M7)</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>38400</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <v>42000</v>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Prestataires externes (missions)</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D23" s="23" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Salaire support/CSM (M16)</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="21" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D24" s="21" t="n">
-        <v>36000</v>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Salaire support/CSM (a partir M25)</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>24000</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Charges sociales (45%)</t>
-        </is>
-      </c>
-      <c r="B25" s="21">
-        <f>(B21+B22+B23+B24)*Hypotheses!B23</f>
-        <v/>
-      </c>
-      <c r="C25" s="21">
-        <f>(C21+C22+C23+C24)*Hypotheses!B23</f>
-        <v/>
-      </c>
-      <c r="D25" s="21">
-        <f>(D21+D22+D23+D24)*Hypotheses!B23</f>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Charges sociales CSM</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="23">
+        <f>D24*Hypotheses!B25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Marketing &amp; acquisition</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C26" s="21" t="n">
-        <v>24000</v>
-      </c>
-      <c r="D26" s="21" t="n">
-        <v>36000</v>
+      <c r="B26" s="23" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C26" s="23" t="n">
+        <v>9600</v>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>14400</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Loyer bureau / coworking</t>
-        </is>
-      </c>
-      <c r="B27" s="21">
-        <f>Hypotheses!B25*12</f>
-        <v/>
-      </c>
-      <c r="C27" s="21">
-        <f>Hypotheses!B25*12*1.5</f>
-        <v/>
-      </c>
-      <c r="D27" s="21">
-        <f>Hypotheses!B25*12*2.5</f>
-        <v/>
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Assurances (RC Pro)</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C27" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Assurances (RC Pro + cyber)</t>
-        </is>
-      </c>
-      <c r="B28" s="21">
-        <f>Hypotheses!B26*12</f>
-        <v/>
-      </c>
-      <c r="C28" s="21" t="n">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Comptable / juridique (fondateur = comptable)</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Materiel / licences</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D29" s="23" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Loyer / coworking (domicile)</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Divers / imprevus</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C31" s="23" t="n">
         <v>2000</v>
       </c>
-      <c r="D28" s="21" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Comptable / juridique</t>
-        </is>
-      </c>
-      <c r="B29" s="21">
-        <f>Hypotheses!B27*12</f>
-        <v/>
-      </c>
-      <c r="C29" s="21" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D29" s="21" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Materiel / licences</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="n">
+      <c r="D31" s="23" t="n">
         <v>3000</v>
       </c>
-      <c r="C30" s="21" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D30" s="21" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Divers / imprevus</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C31" s="21" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D31" s="21" t="n">
-        <v>4000</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Total charges fixes</t>
         </is>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="14">
         <f>SUM(B21:B31)</f>
         <v/>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="14">
         <f>SUM(C21:C31)</f>
         <v/>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="14">
         <f>SUM(D21:D31)</f>
         <v/>
       </c>
@@ -2126,88 +2140,88 @@
           <t>RESULTAT D'EXPLOITATION</t>
         </is>
       </c>
-      <c r="B34" s="21">
+      <c r="B34" s="23">
         <f>B17-B32</f>
         <v/>
       </c>
-      <c r="C34" s="21">
+      <c r="C34" s="23">
         <f>C17-C32</f>
         <v/>
       </c>
-      <c r="D34" s="21">
+      <c r="D34" s="23">
         <f>D17-D32</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Charges financieres</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="n">
-        <v>900</v>
-      </c>
-      <c r="C35" s="21" t="n">
-        <v>750</v>
-      </c>
-      <c r="D35" s="21" t="n">
-        <v>600</v>
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Charges financieres (interets emprunts)</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="n">
+        <v>375</v>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>625</v>
+      </c>
+      <c r="D35" s="23" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>RESULTAT COURANT</t>
         </is>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="23">
         <f>B34-B35</f>
         <v/>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="23">
         <f>C34-C35</f>
         <v/>
       </c>
-      <c r="D36" s="21">
+      <c r="D36" s="23">
         <f>D34-D35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>IS (15%/25%)</t>
         </is>
       </c>
-      <c r="B37" s="21">
-        <f>IF(B36&lt;=0,0,IF(B36&lt;=42500,B36*Hypotheses!B32,42500*Hypotheses!B32+(B36-42500)*Hypotheses!B33))</f>
-        <v/>
-      </c>
-      <c r="C37" s="21">
-        <f>IF(C36&lt;=0,0,IF(C36&lt;=42500,C36*Hypotheses!B32,42500*Hypotheses!B32+(C36-42500)*Hypotheses!B33))</f>
-        <v/>
-      </c>
-      <c r="D37" s="21">
-        <f>IF(D36&lt;=0,0,IF(D36&lt;=42500,D36*Hypotheses!B32,42500*Hypotheses!B32+(D36-42500)*Hypotheses!B33))</f>
+      <c r="B37" s="23">
+        <f>IF(B36&lt;=0,0,IF(B36&lt;=42500,B36*Hypotheses!B33,42500*Hypotheses!B33+(B36-42500)*Hypotheses!B34))</f>
+        <v/>
+      </c>
+      <c r="C37" s="23">
+        <f>IF(C36&lt;=0,0,IF(C36&lt;=42500,C36*Hypotheses!B33,42500*Hypotheses!B33+(C36-42500)*Hypotheses!B34))</f>
+        <v/>
+      </c>
+      <c r="D37" s="23">
+        <f>IF(D36&lt;=0,0,IF(D36&lt;=42500,D36*Hypotheses!B33,42500*Hypotheses!B33+(D36-42500)*Hypotheses!B34))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>RESULTAT NET</t>
         </is>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="14">
         <f>B36-B37</f>
         <v/>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="14">
         <f>C36-C37</f>
         <v/>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="14">
         <f>D36-D37</f>
         <v/>
       </c>
@@ -2218,15 +2232,15 @@
           <t>CAF (Resultat + amortissements)</t>
         </is>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="23">
         <f>B38+1500</f>
         <v/>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="23">
         <f>C38+1500</f>
         <v/>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="23">
         <f>D38+1500</f>
         <v/>
       </c>
@@ -2247,10 +2261,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2269,7 +2283,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PLAN DE TRESORERIE MENSUEL — ANNEE 1</t>
+          <t>PLAN DE TRESORERIE MENSUEL — ANNEE 1 (base 40K, sans NACRE)</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2356,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>ENCAISSEMENTS</t>
         </is>
@@ -2354,55 +2368,55 @@
           <t>CA TTC (MRR x 1.2)</t>
         </is>
       </c>
-      <c r="B5" s="11">
-        <f>'Clients &amp; MRR'!E5*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="C5" s="11">
-        <f>'Clients &amp; MRR'!E6*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="D5" s="11">
-        <f>'Clients &amp; MRR'!E7*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="E5" s="11">
-        <f>'Clients &amp; MRR'!E8*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="F5" s="11">
-        <f>'Clients &amp; MRR'!E9*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>'Clients &amp; MRR'!E10*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="H5" s="11">
-        <f>'Clients &amp; MRR'!E11*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="I5" s="11">
-        <f>'Clients &amp; MRR'!E12*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="J5" s="11">
-        <f>'Clients &amp; MRR'!E13*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="K5" s="11">
-        <f>'Clients &amp; MRR'!E14*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="L5" s="11">
-        <f>'Clients &amp; MRR'!E15*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="M5" s="11">
-        <f>'Clients &amp; MRR'!E16*(1+Hypotheses!B31)</f>
-        <v/>
-      </c>
-      <c r="N5" s="20">
+      <c r="B5" s="12">
+        <f>'Clients &amp; MRR'!E5*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="C5" s="12">
+        <f>'Clients &amp; MRR'!E6*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="D5" s="12">
+        <f>'Clients &amp; MRR'!E7*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="E5" s="12">
+        <f>'Clients &amp; MRR'!E8*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="F5" s="12">
+        <f>'Clients &amp; MRR'!E9*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="G5" s="12">
+        <f>'Clients &amp; MRR'!E10*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="H5" s="12">
+        <f>'Clients &amp; MRR'!E11*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="I5" s="12">
+        <f>'Clients &amp; MRR'!E12*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="J5" s="12">
+        <f>'Clients &amp; MRR'!E13*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="K5" s="12">
+        <f>'Clients &amp; MRR'!E14*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="L5" s="12">
+        <f>'Clients &amp; MRR'!E15*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="M5" s="12">
+        <f>'Clients &amp; MRR'!E16*(1+Hypotheses!B32)</f>
+        <v/>
+      </c>
+      <c r="N5" s="22">
         <f>SUM(B5:M5)</f>
         <v/>
       </c>
@@ -2413,10 +2427,10 @@
           <t>Pret honneur Initiative 95</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="22" t="n">
         <v>15000</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="22">
         <f>SUM(B6:M6)</f>
         <v/>
       </c>
@@ -2424,939 +2438,780 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pret honneur WILCO</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>30000</v>
-      </c>
-      <c r="N7" s="20">
+          <t>Pret bancaire (garanti BPI)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="N7" s="22">
         <f>SUM(B7:M7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pret bancaire</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>30000</v>
-      </c>
-      <c r="N8" s="20">
-        <f>SUM(B8:M8)</f>
-        <v/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>NACRE phase 2 (OPTIONNEL)</t>
+        </is>
+      </c>
+      <c r="N8" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NACRE phase 2</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>10000</v>
-      </c>
-      <c r="N9" s="20">
-        <f>SUM(B9:M9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>TOTAL ENCAISSEMENTS</t>
         </is>
       </c>
-      <c r="B10" s="13">
-        <f>SUM(B5:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="13">
-        <f>SUM(C5:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="13">
-        <f>SUM(D5:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="13">
-        <f>SUM(E5:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="13">
-        <f>SUM(F5:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="13">
-        <f>SUM(G5:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="13">
-        <f>SUM(H5:H9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="13">
-        <f>SUM(I5:I9)</f>
-        <v/>
-      </c>
-      <c r="J10" s="13">
-        <f>SUM(J5:J9)</f>
-        <v/>
-      </c>
-      <c r="K10" s="13">
-        <f>SUM(K5:K9)</f>
-        <v/>
-      </c>
-      <c r="L10" s="13">
-        <f>SUM(L5:L9)</f>
-        <v/>
-      </c>
-      <c r="M10" s="13">
-        <f>SUM(M5:M9)</f>
-        <v/>
-      </c>
-      <c r="N10" s="13">
-        <f>SUM(N5:N9)</f>
-        <v/>
+      <c r="B9" s="14">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="14">
+        <f>SUM(C5:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="14">
+        <f>SUM(D5:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>SUM(E5:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="14">
+        <f>SUM(F5:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="14">
+        <f>SUM(G5:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="14">
+        <f>SUM(H5:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="14">
+        <f>SUM(I5:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="14">
+        <f>SUM(J5:J8)</f>
+        <v/>
+      </c>
+      <c r="K9" s="14">
+        <f>SUM(K5:K8)</f>
+        <v/>
+      </c>
+      <c r="L9" s="14">
+        <f>SUM(L5:L8)</f>
+        <v/>
+      </c>
+      <c r="M9" s="14">
+        <f>SUM(M5:M8)</f>
+        <v/>
+      </c>
+      <c r="N9" s="14">
+        <f>SUM(N5:N8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>DECAISSEMENTS</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>DECAISSEMENTS</t>
-        </is>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Hebergement cloud</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>225</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>225</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="N12" s="12">
+        <f>SUM(B12:M12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Hebergement cloud</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Services tiers (Anthropic/Twilio/Resend)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>175</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>225</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>275</v>
+      </c>
+      <c r="H13" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="I13" s="12" t="n">
+        <v>325</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>375</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>375</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="N13" s="12">
+        <f>SUM(B13:M13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Commissions Stripe</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>213</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>234</v>
+      </c>
+      <c r="N14" s="12">
+        <f>SUM(B14:M14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Salaire fondateur net (M7-M12)</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="M15" s="26" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N15" s="12">
+        <f>SUM(B15:M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Charges sociales fondateur</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>540</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>540</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>540</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>540</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>540</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>540</v>
+      </c>
+      <c r="N16" s="12">
+        <f>SUM(B16:M16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="G17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="H17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="L17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="N13" s="11">
-        <f>SUM(B13:M13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Services tiers</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>250</v>
-      </c>
-      <c r="D14" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <v>300</v>
       </c>
-      <c r="E14" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>400</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <v>400</v>
-      </c>
-      <c r="H14" s="11" t="n">
-        <v>450</v>
-      </c>
-      <c r="I14" s="11" t="n">
+      <c r="N17" s="12">
+        <f>SUM(B17:M17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Assurances (RC Pro)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="N18" s="12">
+        <f>SUM(B18:M18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Materiel</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="J14" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="L14" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="M14" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="N14" s="11">
-        <f>SUM(B14:M14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Commissions Stripe</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>65</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="H15" s="11" t="n">
+      <c r="C19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="12">
+        <f>SUM(B19:M19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Remboursement emprunts</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>728</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>728</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>728</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>728</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>728</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>728</v>
+      </c>
+      <c r="N20" s="12">
+        <f>SUM(B20:M20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TVA a reverser</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>800</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N21" s="12">
+        <f>SUM(B21:M21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Divers / imprevus</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="I15" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>145</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>170</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>195</v>
-      </c>
-      <c r="M15" s="11" t="n">
-        <v>225</v>
-      </c>
-      <c r="N15" s="11">
-        <f>SUM(B15:M15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Salaire fondateur net</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M16" s="24" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N16" s="11">
-        <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Salaire dev net</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="L17" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="M17" s="11" t="n">
-        <v>2500</v>
-      </c>
-      <c r="N17" s="11">
-        <f>SUM(B17:M17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Salaire commercial net</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="L18" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M18" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N18" s="11">
-        <f>SUM(B18:M18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Charges sociales</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>900</v>
-      </c>
-      <c r="C19" s="11" t="n">
-        <v>900</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>900</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>2925</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>2925</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>2925</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>2925</v>
-      </c>
-      <c r="L19" s="11" t="n">
-        <v>2925</v>
-      </c>
-      <c r="M19" s="11" t="n">
-        <v>2925</v>
-      </c>
-      <c r="N19" s="11">
-        <f>SUM(B19:M19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M20" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N20" s="11">
-        <f>SUM(B20:M20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Loyer/coworking</t>
-        </is>
-      </c>
-      <c r="B21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="C21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="D21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="E21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="F21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="H21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="I21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="J21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="K21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="L21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="M21" s="24" t="n">
-        <v>300</v>
-      </c>
-      <c r="N21" s="11">
-        <f>SUM(B21:M21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Assurances</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="C22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="D22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="E22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="F22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="G22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="H22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="I22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="J22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="K22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="L22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="M22" s="24" t="n">
-        <v>125</v>
-      </c>
-      <c r="N22" s="11">
+      <c r="C22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="N22" s="12">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Comptable/juridique</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="C23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="D23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="E23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="F23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="G23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="H23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="I23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="J23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="K23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="L23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="M23" s="24" t="n">
-        <v>250</v>
-      </c>
-      <c r="N23" s="11">
-        <f>SUM(B23:M23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Materiel</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="11">
-        <f>SUM(B24:M24)</f>
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL DECAISSEMENTS</t>
+        </is>
+      </c>
+      <c r="B23" s="14">
+        <f>SUM(B12:B22)</f>
+        <v/>
+      </c>
+      <c r="C23" s="14">
+        <f>SUM(C12:C22)</f>
+        <v/>
+      </c>
+      <c r="D23" s="14">
+        <f>SUM(D12:D22)</f>
+        <v/>
+      </c>
+      <c r="E23" s="14">
+        <f>SUM(E12:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>SUM(F12:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>SUM(G12:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="14">
+        <f>SUM(H12:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>SUM(I12:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>SUM(J12:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>SUM(K12:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>SUM(L12:L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="14">
+        <f>SUM(M12:M22)</f>
+        <v/>
+      </c>
+      <c r="N23" s="14">
+        <f>SUM(N12:N22)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Remboursement emprunts</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="11" t="n">
-        <v>575</v>
-      </c>
-      <c r="I25" s="11" t="n">
-        <v>575</v>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>575</v>
-      </c>
-      <c r="K25" s="11" t="n">
-        <v>575</v>
-      </c>
-      <c r="L25" s="11" t="n">
-        <v>575</v>
-      </c>
-      <c r="M25" s="11" t="n">
-        <v>575</v>
-      </c>
-      <c r="N25" s="11">
-        <f>SUM(B25:M25)</f>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SOLDE DU MOIS</t>
+        </is>
+      </c>
+      <c r="B25" s="24">
+        <f>B9-B23</f>
+        <v/>
+      </c>
+      <c r="C25" s="24">
+        <f>C9-C23</f>
+        <v/>
+      </c>
+      <c r="D25" s="24">
+        <f>D9-D23</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>E9-E23</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
+        <f>F9-F23</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>G9-G23</f>
+        <v/>
+      </c>
+      <c r="H25" s="24">
+        <f>H9-H23</f>
+        <v/>
+      </c>
+      <c r="I25" s="24">
+        <f>I9-I23</f>
+        <v/>
+      </c>
+      <c r="J25" s="24">
+        <f>J9-J23</f>
+        <v/>
+      </c>
+      <c r="K25" s="24">
+        <f>K9-K23</f>
+        <v/>
+      </c>
+      <c r="L25" s="24">
+        <f>L9-L23</f>
+        <v/>
+      </c>
+      <c r="M25" s="24">
+        <f>M9-M23</f>
+        <v/>
+      </c>
+      <c r="N25" s="24">
+        <f>N9-N23</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>TVA a reverser</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="L26" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M26" s="11" t="n">
-        <v>1500</v>
-      </c>
-      <c r="N26" s="11">
-        <f>SUM(B26:M26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL DECAISSEMENTS</t>
-        </is>
-      </c>
-      <c r="B27" s="13">
-        <f>SUM(B13:B26)</f>
-        <v/>
-      </c>
-      <c r="C27" s="13">
-        <f>SUM(C13:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="13">
-        <f>SUM(D13:D26)</f>
-        <v/>
-      </c>
-      <c r="E27" s="13">
-        <f>SUM(E13:E26)</f>
-        <v/>
-      </c>
-      <c r="F27" s="13">
-        <f>SUM(F13:F26)</f>
-        <v/>
-      </c>
-      <c r="G27" s="13">
-        <f>SUM(G13:G26)</f>
-        <v/>
-      </c>
-      <c r="H27" s="13">
-        <f>SUM(H13:H26)</f>
-        <v/>
-      </c>
-      <c r="I27" s="13">
-        <f>SUM(I13:I26)</f>
-        <v/>
-      </c>
-      <c r="J27" s="13">
-        <f>SUM(J13:J26)</f>
-        <v/>
-      </c>
-      <c r="K27" s="13">
-        <f>SUM(K13:K26)</f>
-        <v/>
-      </c>
-      <c r="L27" s="13">
-        <f>SUM(L13:L26)</f>
-        <v/>
-      </c>
-      <c r="M27" s="13">
-        <f>SUM(M13:M26)</f>
-        <v/>
-      </c>
-      <c r="N27" s="13">
-        <f>SUM(N13:N26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>SOLDE DU MOIS</t>
-        </is>
-      </c>
-      <c r="B29" s="22">
-        <f>B10-B27</f>
-        <v/>
-      </c>
-      <c r="C29" s="22">
-        <f>C10-C27</f>
-        <v/>
-      </c>
-      <c r="D29" s="22">
-        <f>D10-D27</f>
-        <v/>
-      </c>
-      <c r="E29" s="22">
-        <f>E10-E27</f>
-        <v/>
-      </c>
-      <c r="F29" s="22">
-        <f>F10-F27</f>
-        <v/>
-      </c>
-      <c r="G29" s="22">
-        <f>G10-G27</f>
-        <v/>
-      </c>
-      <c r="H29" s="22">
-        <f>H10-H27</f>
-        <v/>
-      </c>
-      <c r="I29" s="22">
-        <f>I10-I27</f>
-        <v/>
-      </c>
-      <c r="J29" s="22">
-        <f>J10-J27</f>
-        <v/>
-      </c>
-      <c r="K29" s="22">
-        <f>K10-K27</f>
-        <v/>
-      </c>
-      <c r="L29" s="22">
-        <f>L10-L27</f>
-        <v/>
-      </c>
-      <c r="M29" s="22">
-        <f>M10-M27</f>
-        <v/>
-      </c>
-      <c r="N29" s="22">
-        <f>N10-N27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>TRESORERIE CUMULEE</t>
         </is>
       </c>
-      <c r="B30" s="26">
-        <f>B29</f>
-        <v/>
-      </c>
-      <c r="C30" s="26">
-        <f>B30+C29</f>
-        <v/>
-      </c>
-      <c r="D30" s="26">
-        <f>C30+D29</f>
-        <v/>
-      </c>
-      <c r="E30" s="26">
-        <f>D30+E29</f>
-        <v/>
-      </c>
-      <c r="F30" s="26">
-        <f>E30+F29</f>
-        <v/>
-      </c>
-      <c r="G30" s="26">
-        <f>F30+G29</f>
-        <v/>
-      </c>
-      <c r="H30" s="26">
-        <f>G30+H29</f>
-        <v/>
-      </c>
-      <c r="I30" s="26">
-        <f>H30+I29</f>
-        <v/>
-      </c>
-      <c r="J30" s="26">
-        <f>I30+J29</f>
-        <v/>
-      </c>
-      <c r="K30" s="26">
-        <f>J30+K29</f>
-        <v/>
-      </c>
-      <c r="L30" s="26">
-        <f>K30+L29</f>
-        <v/>
-      </c>
-      <c r="M30" s="26">
-        <f>L30+M29</f>
+      <c r="B26" s="28">
+        <f>B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="28">
+        <f>B26+C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="28">
+        <f>C26+D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="28">
+        <f>D26+E25</f>
+        <v/>
+      </c>
+      <c r="F26" s="28">
+        <f>E26+F25</f>
+        <v/>
+      </c>
+      <c r="G26" s="28">
+        <f>F26+G25</f>
+        <v/>
+      </c>
+      <c r="H26" s="28">
+        <f>G26+H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="28">
+        <f>H26+I25</f>
+        <v/>
+      </c>
+      <c r="J26" s="28">
+        <f>I26+J25</f>
+        <v/>
+      </c>
+      <c r="K26" s="28">
+        <f>J26+K25</f>
+        <v/>
+      </c>
+      <c r="L26" s="28">
+        <f>K26+L25</f>
+        <v/>
+      </c>
+      <c r="M26" s="28">
+        <f>L26+M25</f>
         <v/>
       </c>
     </row>
@@ -3391,6 +3246,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Seuil atteint a ~50 clients (M6-M7, fin S1)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
@@ -3410,39 +3272,39 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Charges fixes totales</t>
         </is>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="23">
         <f>'Compte Resultat'!B32</f>
         <v/>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="23">
         <f>'Compte Resultat'!C32</f>
         <v/>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="23">
         <f>'Compte Resultat'!D32</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Taux de marge sur couts variables</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="29">
         <f>'Compte Resultat'!B18</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="29">
         <f>'Compte Resultat'!C18</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>'Compte Resultat'!D18</f>
         <v/>
       </c>
@@ -3453,123 +3315,124 @@
           <t>SEUIL DE RENTABILITE (CA HT)</t>
         </is>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="23">
         <f>B4/B5</f>
         <v/>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="23">
         <f>C4/C5</f>
         <v/>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="23">
         <f>D4/D5</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Seuil mensuel</t>
         </is>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="23">
         <f>B6/12</f>
         <v/>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="23">
         <f>C6/12</f>
         <v/>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="23">
         <f>D6/12</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Nb clients equivalent (ARPA)</t>
         </is>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="30">
         <f>B7/Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="30">
         <f>C7/Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="30">
         <f>D7/Hypotheses!B11</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr"/>
-      <c r="B9" s="21" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr"/>
-      <c r="D9" s="21" t="inlineStr"/>
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="23" t="inlineStr"/>
+      <c r="C9" s="23" t="inlineStr"/>
+      <c r="D9" s="23" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>CA previsionnel</t>
         </is>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="23">
         <f>'Compte Resultat'!B9</f>
         <v/>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="23">
         <f>'Compte Resultat'!C9</f>
         <v/>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="23">
         <f>'Compte Resultat'!D9</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Marge de securite (CA - Seuil)</t>
         </is>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="23">
         <f>B10-B6</f>
         <v/>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="23">
         <f>C10-C6</f>
         <v/>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="23">
         <f>D10-D6</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Taux de marge de securite</t>
         </is>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="29">
         <f>B11/B10</f>
         <v/>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="29">
         <f>C11/C10</f>
         <v/>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="29">
         <f>D11/D10</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3645,235 +3508,203 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Immobilisations incorporelles (net)</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="12" t="n">
         <v>13500</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="12" t="n">
         <v>12000</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="12" t="n">
         <v>10500</v>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Capital social (SASU)</t>
         </is>
       </c>
-      <c r="F4" s="21" t="n">
+      <c r="F4" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="21" t="n">
+      <c r="G4" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="21" t="n">
+      <c r="H4" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Immobilisations corporelles (net)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D5" s="11" t="n">
+      <c r="B5" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C5" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="D5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Reserves</t>
         </is>
       </c>
-      <c r="F5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="21">
-        <f>-'Compte Resultat'!B38</f>
-        <v/>
-      </c>
-      <c r="H5" s="21">
+      <c r="F5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="23">
+        <f>'Compte Resultat'!B38</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
         <f>F5+'Compte Resultat'!C38</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Creances clients</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="B6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Resultat de l'exercice</t>
         </is>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="23">
         <f>'Compte Resultat'!B38</f>
         <v/>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="23">
         <f>'Compte Resultat'!C38</f>
         <v/>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="23">
         <f>'Compte Resultat'!D38</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Tresorerie</t>
         </is>
       </c>
-      <c r="B7" s="11">
-        <f>'Tresorerie M1-M12'!M30</f>
-        <v/>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>28874</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>135799</v>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Emprunts LT (bancaire)</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>26550</v>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>20100</v>
-      </c>
-      <c r="H7" s="21" t="n">
-        <v>13650</v>
+      <c r="B7" s="12">
+        <f>'Tresorerie M1-M12'!M26</f>
+        <v/>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>240000</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Emprunts LT</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>35632</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>25780</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>15928</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>TOTAL ACTIF</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <f>SUM(B4:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <f>SUM(C4:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="14">
         <f>SUM(D4:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Prets d'honneur (I95 + WILCO)</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>45000</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>45000</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Dettes fournisseurs</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G9" s="21" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H9" s="21" t="n">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Dettes fiscales/sociales</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>6664</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>16614</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>26224</v>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Dettes courantes</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>9651</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>13727</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>14396</v>
       </c>
     </row>
     <row r="11">
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>TOTAL PASSIF</t>
         </is>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>SUM(F4:F10)</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>SUM(G4:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <f>SUM(H4:H10)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Verification Actif = Passif</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>Ecart</t>
         </is>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="31">
         <f>B8-F11</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="31">
         <f>C8-G11</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="31">
         <f>D8-H11</f>
         <v/>
       </c>
@@ -3893,7 +3724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3912,7 +3743,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Hypothese : 30% de clients en moins, charges ajustees</t>
+          <t>Hypothese : 30% de clients en moins, charges ajustees a la baisse</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3766,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Facteur reduction acquisition</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
+      <c r="B5" s="32" t="n">
         <v>0.7</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -3955,15 +3786,15 @@
           <t>Clients fin annee</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="19">
         <f>ROUND('Clients &amp; MRR'!D17*$B$5,0)</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="19">
         <f>ROUND('Clients &amp; MRR'!B22*$B$5,0)</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="19">
         <f>ROUND('Clients &amp; MRR'!B28*$B$5,0)</f>
         <v/>
       </c>
@@ -3974,15 +3805,15 @@
           <t>MRR fin annee</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="12">
         <f>B7*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="12">
         <f>C7*Hypotheses!B11</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="12">
         <f>D7*Hypotheses!B11</f>
         <v/>
       </c>
@@ -3990,83 +3821,83 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>CA HT</t>
-        </is>
-      </c>
-      <c r="B9" s="11">
+          <t>CA HT (pessimiste)</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
         <f>'Compte Resultat'!B9*$B$5</f>
         <v/>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <f>'Compte Resultat'!C9*$B$5</f>
         <v/>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <f>'Compte Resultat'!D9*$B$5</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Charges totales</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>102850</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>260780</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>363800</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Charges totales (ajustees)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>20100</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>62600</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>120800</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Resultat net</t>
-        </is>
-      </c>
-      <c r="B11" s="21">
+          <t>Resultat net (pessimiste)</t>
+        </is>
+      </c>
+      <c r="B11" s="23">
         <f>B9-B10</f>
         <v/>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="23">
         <f>C9-C10</f>
         <v/>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="23">
         <f>D9-D10</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Tresorerie fin annee</t>
         </is>
       </c>
-      <c r="B13" s="32" t="n">
-        <v>30612</v>
-      </c>
-      <c r="C13" s="32">
+      <c r="B13" s="33" t="n">
+        <v>47200</v>
+      </c>
+      <c r="C13" s="33">
         <f>B13+C11</f>
         <v/>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <f>C13+D11</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Actions correctives si scenario pessimiste :</t>
         </is>
@@ -4075,14 +3906,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>→ Reduction marketing de 30%</t>
+          <t>→ Reduction marketing de 50%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>→ Report recrutement commercial de 3 mois</t>
+          <t>→ Reduction salaire fondateur temporairement</t>
         </is>
       </c>
     </row>
@@ -4090,6 +3921,20 @@
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>→ Negociation report echeance prets d'honneur</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>→ Missions freelance en parallele pour le fondateur</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>→ Tresorerie reste POSITIVE meme a -30% (modele frugal)</t>
         </is>
       </c>
     </row>
@@ -4110,10 +3955,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -4167,317 +4012,289 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Pret honneur Initiative 95</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>5 ans</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="12">
         <f>B4/54</f>
         <v/>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Pret honneur WILCO</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Pret bancaire (garanti BPI 60%)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>5 ans</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>NACRE phase 2 (beneficiaire ASS)</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>5 ans</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>12 mois</t>
         </is>
       </c>
-      <c r="F5" s="11">
-        <f>B5/54</f>
-        <v/>
-      </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="F6" s="12">
+        <f>B6/48</f>
+        <v/>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>M13</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Pret bancaire (garanti BPI)</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>5 ans</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>575</v>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>M7</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>NACRE phase 2</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>5 ans</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>12 mois</t>
-        </is>
-      </c>
-      <c r="F7" s="11">
-        <f>B7/54</f>
-        <v/>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="13">
-        <f>SUM(B4:B7)</f>
-        <v/>
-      </c>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="13" t="n"/>
+      <c r="B7" s="14">
+        <f>SUM(B4:B6)</f>
+        <v/>
+      </c>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>ECHEANCIER ANNUEL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>ECHEANCIER ANNUEL</t>
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>An 1</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>An 2</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>An 3</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>An 1</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>An 2</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>An 3</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Remb. pret I95</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
+        <f>F4*6</f>
+        <v/>
+      </c>
+      <c r="C11" s="12">
+        <f>F4*12</f>
+        <v/>
+      </c>
+      <c r="D11" s="12">
+        <f>F4*12</f>
+        <v/>
+      </c>
+      <c r="E11" s="12">
+        <f>SUM(B11:D11)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Remb. pret I95</t>
-        </is>
-      </c>
-      <c r="B12" s="11">
-        <f>F4*6</f>
-        <v/>
-      </c>
-      <c r="C12" s="11">
-        <f>F4*12</f>
-        <v/>
-      </c>
-      <c r="D12" s="11">
-        <f>F4*12</f>
-        <v/>
-      </c>
-      <c r="E12" s="11">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Remb. pret bancaire</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>6*450</f>
+        <v/>
+      </c>
+      <c r="C12" s="12">
+        <f>12*450</f>
+        <v/>
+      </c>
+      <c r="D12" s="12">
+        <f>12*450</f>
+        <v/>
+      </c>
+      <c r="E12" s="12">
         <f>SUM(B12:D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Remb. pret WILCO</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="11">
-        <f>F5*12</f>
-        <v/>
-      </c>
-      <c r="D13" s="11">
-        <f>F5*12</f>
-        <v/>
-      </c>
-      <c r="E13" s="11">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Remb. NACRE</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12">
+        <f>F6*12</f>
+        <v/>
+      </c>
+      <c r="D13" s="12">
+        <f>F6*12</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
         <f>SUM(B13:D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Remb. pret bancaire</t>
-        </is>
-      </c>
-      <c r="B14" s="11">
-        <f>6*575</f>
-        <v/>
-      </c>
-      <c r="C14" s="11">
-        <f>12*575</f>
-        <v/>
-      </c>
-      <c r="D14" s="11">
-        <f>12*575</f>
-        <v/>
-      </c>
-      <c r="E14" s="11">
-        <f>SUM(B14:D14)</f>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL REMBOURSEMENTS</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <f>SUM(B11:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="14">
+        <f>SUM(C11:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="14">
+        <f>SUM(D11:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>SUM(E11:E13)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Remb. NACRE</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="11">
-        <f>F7*12</f>
-        <v/>
-      </c>
-      <c r="D15" s="11">
-        <f>F7*12</f>
-        <v/>
-      </c>
-      <c r="E15" s="11">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Dont interets (pret bancaire)</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>375</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>625</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>500</v>
+      </c>
+      <c r="E15" s="22">
         <f>SUM(B15:D15)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL REMBOURSEMENTS</t>
-        </is>
-      </c>
-      <c r="B16" s="13">
-        <f>SUM(B12:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="13">
-        <f>SUM(C12:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="13">
-        <f>SUM(D12:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="13">
-        <f>SUM(E12:E15)</f>
-        <v/>
-      </c>
-    </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Dont interets</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="n">
-        <v>450</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <v>900</v>
-      </c>
-      <c r="D17" s="20" t="n">
-        <v>600</v>
-      </c>
-      <c r="E17" s="20">
-        <f>SUM(B17:D17)</f>
-        <v/>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>RESUME REMBOURSEMENTS MENSUELS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>M1-M6 : aucun remboursement (differe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>M7-M12 : 728 EUR/mois (I95 278 + bancaire 450)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>M13+ : 821 EUR/mois (+ NACRE 93)</t>
+        </is>
       </c>
     </row>
   </sheetData>
